--- a/paymentlist.xlsx
+++ b/paymentlist.xlsx
@@ -425,16 +425,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="7"/>
     <col customWidth="1" max="2" min="2" width="8"/>
     <col customWidth="1" max="3" min="3" width="20"/>
     <col customWidth="1" max="4" min="4" width="20"/>
-    <col customWidth="1" max="5" min="5" width="25"/>
+    <col customWidth="1" max="5" min="5" width="20"/>
     <col customWidth="1" max="6" min="6" width="15"/>
     <col customWidth="1" max="7" min="7" width="15"/>
+    <col customWidth="1" max="8" min="8" width="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +466,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Amount</t>
         </is>
       </c>
@@ -500,7 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8,000</t>
         </is>
       </c>
     </row>
@@ -535,7 +546,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>32,000</t>
         </is>
       </c>
     </row>
@@ -570,6 +586,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>10,000</t>
         </is>
       </c>
@@ -605,6 +626,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>10,000</t>
         </is>
       </c>
@@ -615,32 +641,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adedoyin</t>
+          <t>Adaigbe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ayokunnumi</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23B Jibewa Shomorin Close</t>
+          <t>7 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2347018028053</t>
+          <t>2348164289106</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5,500</t>
+          <t>08.01/2025</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -675,7 +706,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,500</t>
         </is>
       </c>
     </row>
@@ -710,6 +746,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>10,000</t>
         </is>
       </c>
@@ -720,32 +761,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adegbite</t>
+          <t>Adedoyin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Ayokunnumi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2 Sam Ogegbo Road</t>
+          <t>23B Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2347059357158</t>
+          <t>2347018028053</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>25/07/2025</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,500</t>
         </is>
       </c>
     </row>
@@ -760,27 +806,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adegboye</t>
+          <t>Adegbite</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adeniyi</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14 Jibewa Shomorin Close</t>
+          <t>2 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2348060227640</t>
+          <t>2347059357158</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>02/02/2025</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -815,7 +866,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>28/09/2025</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7,500</t>
         </is>
       </c>
     </row>
@@ -830,27 +886,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adekanmbi</t>
+          <t>Adegboye</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tokunboh</t>
+          <t>Adeniyi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11 Sam Ogegbo Road</t>
+          <t>14 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2348023273866</t>
+          <t>2348060227640</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -885,7 +946,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,000</t>
         </is>
       </c>
     </row>
@@ -900,27 +966,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adelaja</t>
+          <t>Adekanmbi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Tokunboh</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>11 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2348133125693</t>
+          <t>2348023273866</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>31/12/2024</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>24,000</t>
         </is>
       </c>
     </row>
@@ -935,25 +1006,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Adeleye</t>
+          <t>Adelaja</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Simileoluwa</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1 Adeogun Street</t>
+          <t>19 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2348102492110</t>
+          <t>2348133125693</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -970,27 +1046,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ademoye </t>
+          <t>Adeleye</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Temitayo</t>
+          <t>Simileoluwa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>1 Adeogun Street</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2348067136212</t>
+          <t>2348102492110</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1005,27 +1086,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Adeniji</t>
+          <t xml:space="preserve">Ademoye </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bayo</t>
+          <t>Temitayo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15 Jibewa Shomorin Close</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2348118062235</t>
+          <t>2348067136212</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>28/09/2025</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6,500</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1146,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8,000</t>
         </is>
       </c>
     </row>
@@ -1075,27 +1166,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Adepitan</t>
+          <t>Adeniji</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t>Bayo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18 Sam Ogegbo Road</t>
+          <t>15 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2348036397591</t>
+          <t>2348118062235</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>32,000</t>
         </is>
       </c>
     </row>
@@ -1110,27 +1206,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Adepitan</t>
+          <t>Adeniyi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t xml:space="preserve">Solomon </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18 Sam Ogegbo Road</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2348036397591</t>
+          <t>2348067155887</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>29/11/2025</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -1145,27 +1246,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adesiyan </t>
+          <t>Adeoti</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajibola </t>
+          <t>David</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2348026792850</t>
+          <t>2349038817804</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1,000</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1286,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adun</t>
+          <t>Adeoti</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ayodele</t>
+          <t>David</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13 Jibewa Shomorin Close</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2348055060581</t>
+          <t>2349038817804</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>9,000</t>
         </is>
       </c>
     </row>
@@ -1215,27 +1326,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Adun</t>
+          <t>Adepitan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ayodele</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13 Jibewa Shomorin Close</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2348055060581</t>
+          <t>2348036397591</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>12/07/2025</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1366,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Afunnize</t>
+          <t>Adepitan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4 Jibewa Shomorin Close</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2348023330391</t>
+          <t>2348036397591</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>12/07/2025</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1,000</t>
         </is>
       </c>
     </row>
@@ -1285,27 +1406,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ajibuwa</t>
+          <t>Adepoju</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gbenga</t>
+          <t>Adeola</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25 Jibewa Shomorin Close</t>
+          <t xml:space="preserve">7 Jibewa Shomorin Close	</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2347036478079</t>
+          <t>2347039229295</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>31/05/2025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>16,800</t>
         </is>
       </c>
     </row>
@@ -1315,32 +1441,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alhaji </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Akingbola</t>
+          <t xml:space="preserve">Adesiyan </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bukky</t>
+          <t xml:space="preserve">Ajibola </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14 Jibewa Shomorin Close</t>
+          <t>19 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2348088396446</t>
+          <t>2348026792850</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>12/07/2025</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1355,27 +1486,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Akinjola</t>
+          <t>Adun</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Adebola</t>
+          <t>Ayodele</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4B Adeogun Street</t>
+          <t>13 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2348029038681</t>
+          <t>2348055060581</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1385,32 +1521,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Akinwande</t>
+          <t>Adun</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Ayodele</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26 Jibewa Shomorin Close</t>
+          <t>13 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2348087183541</t>
+          <t>2348055060581</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>30/05/2025</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1425,27 +1566,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Akpan</t>
+          <t>Afunnize</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sylvanus</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>4 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2348061699107</t>
+          <t>2348023330391</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>27/02/2025</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -1460,25 +1606,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aladeloba</t>
+          <t>Ajibuwa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adeyinka</t>
+          <t>Gbenga</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>25 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2348033676290</t>
+          <t>2347036478079</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -1490,32 +1641,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Alhaji </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alaga</t>
+          <t>Akingbola</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ifeoluwa</t>
+          <t>Bukky</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8 Sam Ogegbo Road</t>
+          <t>14 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2348138134363</t>
+          <t>2348088396446</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12,800</t>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -1525,32 +1681,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alawonde</t>
+          <t>Akinjola</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elizabeth </t>
+          <t>Adebola</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22 Jibewa Shomorin Close</t>
+          <t>4B Adeogun Street</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2348039096600</t>
+          <t>2348029038681</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>19/03/2025</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -1560,30 +1721,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Akinwande</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Onibode</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5 Sam Ogegbo Road</t>
+          <t>26 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2349091974294</t>
+          <t>2348087183541</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
+        <is>
+          <t>24/01/2025</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
@@ -1600,27 +1766,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ambali</t>
+          <t>Akpan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lekan</t>
+          <t>Sylvanus</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2348034688604</t>
+          <t>2348061699107</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -1630,32 +1801,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Anifowose A .O</t>
+          <t>Akpan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Abiola</t>
+          <t>Sylvanus</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2348023421342</t>
+          <t>2348061699107</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -1665,32 +1841,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Anyawu</t>
+          <t>Aladeloba</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hilda</t>
+          <t xml:space="preserve"> Adeyinka</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Road</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2348034119127</t>
+          <t>2348033676290</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>12/07/2025</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1700,32 +1881,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Asuquo</t>
+          <t>Alaga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Ifeoluwa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>8 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2348038301804</t>
+          <t>2348138134363</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>01/03/2025</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>12,800</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1921,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mrs </t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Asuquo</t>
+          <t>Alawonde</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1750,17 +1936,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
+          <t>22 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2348033381761</t>
+          <t>2348039096600</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>23/01/2025</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1775,27 +1966,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Awotunde</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Abayomi</t>
+          <t>Onibode</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>5 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2348023171758</t>
+          <t>2349091974294</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>12/03/2025</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -1810,27 +2006,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Awotunde</t>
+          <t>Ambali</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Abayomi</t>
+          <t>Lekan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2348023171758</t>
+          <t>2348034688604</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1845,27 +2046,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Awoyemi</t>
+          <t>Ambali</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Olusegun</t>
+          <t>Lekan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3 Victorious Avenue</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2348074736472</t>
+          <t>2348034688604</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>24/03/2025</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1875,32 +2081,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ayeleso </t>
+          <t>Andy</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Oluwatosin</t>
+          <t>Anyakpo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7A Sam Ogegbo Road</t>
+          <t>7 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2348039260661</t>
+          <t>2348023416950</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1915,27 +2126,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ayinuola</t>
+          <t>Anifowose</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Abiola</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6 Sam Ogegbo Road</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2348033041514</t>
+          <t>2348023421342</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1950,27 +2166,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ayinuola</t>
+          <t>Anifowose</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Abiola</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6 Sam Ogegbo Road</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2348033041514</t>
+          <t>2348023421342</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1980,30 +2201,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ayodeji</t>
+          <t>Anyawu</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aro</t>
+          <t>Hilda</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16 Jibewa Shomorin Close</t>
+          <t>3 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2348035669330</t>
+          <t>2348034119127</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
+        <is>
+          <t>31/05/2025</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>16,000</t>
         </is>
@@ -2015,32 +2241,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mrs </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ayodeji</t>
+          <t>Asuquo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aro</t>
+          <t xml:space="preserve">Elizabeth </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16 Jibewa Shomorin Close</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2348035669330</t>
+          <t>2348033381761</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -2050,32 +2281,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mrs </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ayodele</t>
+          <t>Asuquo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sylvester</t>
+          <t xml:space="preserve">Elizabeth </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19 Victorious Avenue</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14375569759</t>
+          <t>2348033381761</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -2090,27 +2326,32 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Baba</t>
+          <t>Asuquo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wale</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2348034449650</t>
+          <t>2348038301804</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2125,27 +2366,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Babatunde</t>
+          <t>Awotunde</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ibukun</t>
+          <t>Abayomi</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2348185177336</t>
+          <t>2348023171758</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>30/12/2024</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -2155,32 +2401,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bakare</t>
+          <t>Awotunde</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Folake</t>
+          <t>Abayomi</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16 Jibewa Shomorin Close</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2348167650124</t>
+          <t>2348023171758</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>13/03/2025</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -2190,32 +2441,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bakare</t>
+          <t>Awoyemi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Folake</t>
+          <t>Olusegun</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16 Jibewa Shomorin Close</t>
+          <t>3 Victorious Avenue</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2348167650124</t>
+          <t>2348074736472</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>03/06/2025</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -2225,32 +2481,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Benyeogor </t>
+          <t xml:space="preserve">Ayeleso </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Micheal</t>
+          <t>Oluwatosin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6 Jibewa Shomorin Close</t>
+          <t>7A Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2347054023503</t>
+          <t>2348039260661</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>26/06/2025</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -2260,32 +2521,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bish</t>
+          <t>Ayinuola</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Bolaji</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>6 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2349032346583</t>
+          <t>2348033041514</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>26/06/2025</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8,000</t>
         </is>
       </c>
     </row>
@@ -2295,32 +2561,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Celestina</t>
+          <t>Ayinuola</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Road</t>
+          <t>6 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2348082896410</t>
+          <t>2348033041514</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>12,800</t>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>32,000</t>
         </is>
       </c>
     </row>
@@ -2330,32 +2601,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Ayodeji</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EREWIVE EWOMA</t>
+          <t>Aro</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>16 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2348036452618</t>
+          <t>2348035669330</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -2370,27 +2646,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dad </t>
+          <t>Ayodeji</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Bright</t>
+          <t>Aro</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>16 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2348033536153</t>
+          <t>2348035669330</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>17/07/2025</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -2400,32 +2681,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dada</t>
+          <t>Ayodele</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Sylvester</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10 Jibewa Shomorin Close</t>
+          <t>19 Victorious Avenue</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>254705913730</t>
+          <t>14375569759</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>24/03/2025</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -2440,27 +2726,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Baba</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paradise</t>
+          <t>Wale</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10 Martins Street</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2349134413661</t>
+          <t>2348034449650</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>24/07/2025</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -2470,32 +2761,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pst</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Davids</t>
+          <t>Babatunde</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Ibukun</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2348053491515</t>
+          <t>2348185177336</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -2505,32 +2801,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pst</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Davids</t>
+          <t>Bakare</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Folake</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>16 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2348053491515</t>
+          <t>2348167650124</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -2540,32 +2841,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dipo</t>
+          <t>Bakare</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ibidunmoye</t>
+          <t>Folake</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>16 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2349055573714</t>
+          <t>2348167650124</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>14/02/2025</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -2575,32 +2881,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Divine</t>
+          <t xml:space="preserve">Benyeogor </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Micheal</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2 Sam Ogegbo Road</t>
+          <t>6 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2348035742187</t>
+          <t>2347054023503</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>23/01/2025</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2615,27 +2926,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Edogun</t>
+          <t>Bish</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Peace</t>
+          <t>Bolaji</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2349168016803</t>
+          <t>2349032346583</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>16/01/2025</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -2645,32 +2961,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dcns</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Celestina</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Osarodion</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20 Sam Ogegbo Road</t>
+          <t>3 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2348034011995</t>
+          <t>2348082896410</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>31/12/2024</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>12,800</t>
         </is>
       </c>
     </row>
@@ -2680,32 +3001,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Etim</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Berryl</t>
+          <t>EREWIVE EWOMA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16 Sam Ogegbo Road</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2348028591146</t>
+          <t>2348036452618</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6,000</t>
         </is>
       </c>
     </row>
@@ -2720,27 +3046,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fayemi</t>
+          <t xml:space="preserve">Dad </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Taiwo</t>
+          <t>Bright</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2348034317485</t>
+          <t>2348033536153</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>29/06/2025</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>13,000</t>
         </is>
       </c>
     </row>
@@ -2750,32 +3081,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fayemi</t>
+          <t>Dada</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Taiwo</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>10 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2348034317485</t>
+          <t>254705913730</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>25,000</t>
         </is>
       </c>
     </row>
@@ -2790,27 +3126,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Akinwunmi</t>
+          <t>Paradise</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>23A Jibewa Shomorin Close</t>
+          <t>10 Martins Street</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2348035651323</t>
+          <t>2349134413661</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -2820,32 +3161,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Filade</t>
+          <t xml:space="preserve">David </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Olumide</t>
+          <t>Osemudiemen</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2348023073320</t>
+          <t>2348134694901</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -2855,32 +3201,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Pst</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Filade</t>
+          <t>Davids</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Olumide</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2348023073320</t>
+          <t>2348053491515</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>18,000</t>
         </is>
       </c>
     </row>
@@ -2890,32 +3241,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Pst</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gbonegun</t>
+          <t>Davids</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>22 Jibewa Shomorin Close</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2348065016641</t>
+          <t>2348053491515</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2,000</t>
         </is>
       </c>
     </row>
@@ -2925,32 +3281,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Dipo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Temitope</t>
+          <t>Ibidunmoye</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2348033193376</t>
+          <t>2349055573714</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>04/05/2025</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2960,32 +3321,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Divine</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18 Jibewa Shomorin Close</t>
+          <t>2 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>16185140886</t>
+          <t>2348035742187</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6,000</t>
         </is>
       </c>
     </row>
@@ -2995,32 +3361,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Edogun</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Peace</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2347061533148</t>
+          <t>2349168016803</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>27/05/2025</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3035,27 +3406,32 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Godwin</t>
+          <t>Enaholo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Nwosu</t>
+          <t>David</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>15 Olanpejo Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2348030964175</t>
+          <t>2348134694901</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -3065,32 +3441,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Igwe</t>
+          <t xml:space="preserve">Enumah </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ebuka</t>
+          <t>Faith</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5 Martins Street</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2348105620740</t>
+          <t>2349060884030</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>04/03/2025</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>6,000</t>
         </is>
       </c>
     </row>
@@ -3100,32 +3481,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Dcns</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Igwe</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Kelechi</t>
+          <t>Osarodion</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20 Jibewa Shomorin Close</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2348022897987</t>
+          <t>2348034011995</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6,000</t>
         </is>
       </c>
     </row>
@@ -3135,32 +3521,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Igwillo</t>
+          <t>Etim</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinton </t>
+          <t>Berryl</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>16 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2348038588597</t>
+          <t>2348028591146</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>12,800</t>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -3170,32 +3561,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iheme</t>
+          <t>Etim</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ekene</t>
+          <t>Berryl</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>16 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2348035007625</t>
+          <t>2348028591146</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>12/03/2025</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3205,32 +3601,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ijamakinwa</t>
+          <t>Fakorede</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Olabode</t>
+          <t xml:space="preserve">Elizabeth </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2347032701075</t>
+          <t>2347065873996</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -3240,32 +3641,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ikeola</t>
+          <t>Fakorede</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Rotimi</t>
+          <t xml:space="preserve">Elizabeth </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>No 7B Sam Ogegbo Road</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2348035677330</t>
+          <t>2347065873996</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>7,000</t>
         </is>
       </c>
     </row>
@@ -3280,27 +3686,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ikeola</t>
+          <t>Fayemi</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Rotimi</t>
+          <t>Taiwo</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>No 7B Sam Ogegbo Road</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2348035677330</t>
+          <t>2348034317485</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>14/02/2025</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -3310,32 +3721,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Iloeje</t>
+          <t>Fayemi</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Kenechukwu</t>
+          <t>Taiwo</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>10 Jibewa Shomorin Close</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2348034960305</t>
+          <t>2348034317485</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>14/02/2025</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -3350,27 +3766,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jimoh</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Koulete</t>
+          <t>Akinwunmi</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>23A Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2349132223243</t>
+          <t>2348035651323</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>04/02/2025</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3380,32 +3801,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jimoh</t>
+          <t>Filade</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Abiodun</t>
+          <t>Olumide</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>9 Victorious Avenue</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2348143798069</t>
+          <t>2348023073320</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>15/01/2025</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>8,000</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3841,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kayode</t>
+          <t>Filade</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Olanbiwonninum</t>
+          <t>Olumide</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2348130853892</t>
+          <t>2348023073320</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>20/07/2025</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -3455,27 +3886,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kougnaglo</t>
+          <t>Gbonegun</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Bartholomew</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>16 Sam Ogegbo Road</t>
+          <t>22 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2348034256298</t>
+          <t>2348065016641</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>12/03/2025</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3490,27 +3926,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kougnaglo</t>
+          <t>George</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Bartholomew</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16 Sam Ogegbo Road</t>
+          <t>18 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2348034256298</t>
+          <t>16185140886</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3520,32 +3961,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>George</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Treasure </t>
+          <t>Temitope</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>6 Olanpejo Street</t>
+          <t>19 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2348057105540</t>
+          <t>2348033193376</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>27/09/2025</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3555,32 +4001,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nifemi</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Eitaio</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>11 Victorious Avenue</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>447411592514</t>
+          <t>2347061533148</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -3590,32 +4041,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr  </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nnorom</t>
+          <t>Godwin</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sylvester</t>
+          <t>Nwosu</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>15 Olanpejo Street</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2348096661124</t>
+          <t>2348030964175</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -3630,27 +4086,32 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Obiayo</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Chiboka</t>
+          <t>Yinusa</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>4A Adeogun Street</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2348038222999</t>
+          <t>2349079864312</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3665,27 +4126,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Obiayo</t>
+          <t>Igwe</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Chiboka</t>
+          <t>Kelechi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>4A Adeogun Street</t>
+          <t>20 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2348038222999</t>
+          <t>2348022897987</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -3695,30 +4161,35 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mrs </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odoguwa </t>
+          <t>Igwe</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Olusola</t>
+          <t>Kelechi</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>20 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2348023431044</t>
+          <t>2348022897987</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
+        <is>
+          <t>24/02/2025</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>16,000</t>
         </is>
@@ -3730,32 +4201,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ms</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ogamba</t>
+          <t>Igwe</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Chioma</t>
+          <t xml:space="preserve"> Ebuka</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>22 Sam Ogegbo Road</t>
+          <t>5 Martins Street</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2347035566619</t>
+          <t>2348105620740</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3765,32 +4241,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Olalekan</t>
+          <t>Igwillo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sakirat</t>
+          <t xml:space="preserve">Clinton </t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2349124065368</t>
+          <t>2348038588597</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>28/04/2025</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>12,800</t>
         </is>
       </c>
     </row>
@@ -3805,27 +4286,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Olaleye</t>
+          <t>Iheme</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Gbenga</t>
+          <t>Ekene</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17 Sam Ogegbo Road</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2348028401202</t>
+          <t>2348035007625</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>19/06/2025</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3840,27 +4326,32 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Olaleye</t>
+          <t>Ijamakinwa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Gbenga</t>
+          <t>Olabode</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17 Sam Ogegbo Road</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2348028401202</t>
+          <t>2347032701075</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>13/07/2025</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -3875,27 +4366,32 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olanpejo </t>
+          <t>Ikeola</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baba Tawa </t>
+          <t>Rotimi</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7 Olanpejo Street</t>
+          <t>No 7B Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2348029083918</t>
+          <t>2348035677330</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>21/01/2025</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3910,27 +4406,32 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olanpejo </t>
+          <t>Ikeola</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baba Tawa </t>
+          <t>Rotimi</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7 Olanpejo Street</t>
+          <t>No 7B Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2348029083918</t>
+          <t>2348035677330</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>01/05/2025</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3940,32 +4441,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Olaoye</t>
+          <t>Iloeje</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Kenechukwu</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>10 Martins Street</t>
+          <t>10 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2348034102329</t>
+          <t>2348034960305</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>19,500</t>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3980,27 +4486,32 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Olaoye</t>
+          <t>Jaywon</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10 Martins Street</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2348034102329</t>
+          <t>2349068400154</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -4010,32 +4521,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pst </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Oloyede</t>
+          <t>Jimoh</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Koulete</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2349083228650</t>
+          <t>2349132223243</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>06/07/2025</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -4045,32 +4561,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Olurankise</t>
+          <t>Jimoh</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Judith</t>
+          <t>Abiodun</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>11 Jibewa Shomorin Close</t>
+          <t>9 Victorious Avenue</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2348036763996</t>
+          <t>2348143798069</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>07/03/2025</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -4085,27 +4606,32 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Omotayo</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>Opeyemi</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19 Jibewa Shomorin Close</t>
+          <t>3 Victorious Avenue</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2348023260295</t>
+          <t>2348033869066</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>08/01/2025</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -4120,27 +4646,32 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Onyeukwu</t>
+          <t>Kayode</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ikechukwu </t>
+          <t>Olanbiwonninum</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>18 Jibewa Shomorin Close</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2348036295974</t>
+          <t>2348130853892</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>25/07/2025</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>3,000</t>
         </is>
       </c>
     </row>
@@ -4150,32 +4681,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Opeyemi</t>
+          <t>Kougnaglo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Akanmu</t>
+          <t>Bartholomew</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1 Adeogun Street</t>
+          <t>16 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2348033635600</t>
+          <t>2348034256298</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>14/03/2025</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -4185,32 +4721,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Osahon</t>
+          <t>Kougnaglo</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lambert </t>
+          <t>Bartholomew</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>8 Jibewa Shomorin Close</t>
+          <t>16 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2348066860123</t>
+          <t>2348034256298</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -4225,27 +4766,32 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Osanyintade</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Temidayo</t>
+          <t xml:space="preserve"> Treasure </t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7A Sam Ogegbo Road</t>
+          <t>6 Olanpejo Street</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2348037125979</t>
+          <t>2348057105540</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>21/01/2025</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>24,000</t>
         </is>
       </c>
     </row>
@@ -4260,27 +4806,32 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Osunkunle</t>
+          <t>Nifemi</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Oluwatobi</t>
+          <t>Eitaio</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>No19A Jibewa Shomorin CloseVictory Estate</t>
+          <t>11 Victorious Avenue</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2349024009331</t>
+          <t>447411592514</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>31/12/2024</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>36,000</t>
         </is>
       </c>
     </row>
@@ -4290,32 +4841,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr  </t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Osunkunle</t>
+          <t>Nnorom</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Oluwatobi</t>
+          <t>Sylvester</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>No19A Jibewa Shomorin CloseVictory Estate</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2349024009331</t>
+          <t>2348096661124</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>22/06/2025</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -4330,27 +4886,32 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Osunleye</t>
+          <t>Obiayo</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ayoola</t>
+          <t>Chiboka</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6 Adeogun Street</t>
+          <t>4A Adeogun Street</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2348134654792</t>
+          <t>2348038222999</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>8,000</t>
         </is>
       </c>
     </row>
@@ -4365,27 +4926,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Otite</t>
+          <t>Obiayo</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fred </t>
+          <t>Chiboka</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>4A Adeogun Street</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2348158169490</t>
+          <t>2348038222999</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>04/03/2025</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>32,000</t>
         </is>
       </c>
     </row>
@@ -4400,27 +4966,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Owolabi</t>
+          <t>Odiana</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Abimbola</t>
+          <t>Soltune</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>13 Sam Ogegbo Road</t>
+          <t>11 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2349163656777</t>
+          <t>2348138146320</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -4430,32 +5001,37 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Mrs </t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Oyalami</t>
+          <t xml:space="preserve">Odoguwa </t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Kemi</t>
+          <t>Olusola</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>4 Jibewa Shomorin Close</t>
+          <t>19 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2348089296998</t>
+          <t>2348023431044</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>30/12/2024</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>16,000</t>
         </is>
       </c>
     </row>
@@ -4465,32 +5041,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Mrs </t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oyelehin</t>
+          <t xml:space="preserve">Odoguwa </t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Oluwatosin</t>
+          <t>Olusola</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>7A Sam Ogegbo Road</t>
+          <t>19 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2348084586119</t>
+          <t>2348023431044</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -4505,27 +5086,32 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oyemah</t>
+          <t>Odukoya</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Oluwatobi</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>21 Sam Ogegbo Road</t>
+          <t>7 Victorious Avenue</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2348153992720</t>
+          <t>2348182024906</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>24/08/2025</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -4535,32 +5121,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Ms</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ronke</t>
+          <t>Ogamba</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Balogun</t>
+          <t>Chioma</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>22 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2348075000362</t>
+          <t>2347035566619</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -4570,30 +5161,35 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Daddy</t>
+          <t xml:space="preserve">Baba </t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Shomorin</t>
+          <t>Ogunjirin</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Jibewa</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>9 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2348023610501</t>
+          <t>2348032400317</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -4605,32 +5201,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Elder </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Soladogun</t>
+          <t>Ojomu</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Arike</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>23B Jibewa Shomorin Close</t>
+          <t>8 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2347018028053</t>
+          <t>2348033253879</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -4645,27 +5246,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Soladogun</t>
+          <t>Olalekan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Arike</t>
+          <t>Sakirat</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>23B Jibewa Shomorin Close</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2347018028053</t>
+          <t>2349124065368</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>25/07/2025</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>3,000</t>
         </is>
       </c>
     </row>
@@ -4675,32 +5281,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Soladogun</t>
+          <t>Olaleye</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Arike</t>
+          <t>Gbenga</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>23B Jibewa Shomorin Close</t>
+          <t>17 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2347018028053</t>
+          <t>2348028401202</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>5,500</t>
+          <t>13/04/2025</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -4710,32 +5321,37 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tokunboh</t>
+          <t>Olaleye</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Daniju</t>
+          <t>Gbenga</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>3 Olanpejo Street</t>
+          <t>17 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2348068687060</t>
+          <t>2348028401202</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -4745,32 +5361,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tokunboh</t>
+          <t xml:space="preserve">Olanpejo </t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Daniju</t>
+          <t xml:space="preserve">Baba Tawa </t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>3 Olanpejo Street</t>
+          <t>7 Olanpejo Street</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2348068687060</t>
+          <t>2348029083918</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>27/09/2025</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>9,000</t>
         </is>
       </c>
     </row>
@@ -4785,27 +5406,32 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolulope </t>
+          <t xml:space="preserve">Olanpejo </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Akinjise</t>
+          <t xml:space="preserve">Baba Tawa </t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>7 Olanpejo Street</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2348169696476</t>
+          <t>2348029083918</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20/02/2025</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>9,000</t>
         </is>
       </c>
     </row>
@@ -4815,32 +5441,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tomisin</t>
+          <t>Olaoye</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Obakpolo</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>10 Martins Street</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2349084860718</t>
+          <t>2348034102329</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>9,800</t>
+          <t>14/05/2025</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>20,500</t>
         </is>
       </c>
     </row>
@@ -4850,32 +5481,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ukaha</t>
+          <t>Olaoye</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Eberechi</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>16 Sam Ogegbo Road</t>
+          <t>10 Martins Street</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2348064383418</t>
+          <t>2348034102329</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>14/05/2025</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>19,500</t>
         </is>
       </c>
     </row>
@@ -4885,32 +5521,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Pst </t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ututu</t>
+          <t>Oloyede</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cletus</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>8 Sam Ogegbo Road</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2348039727477</t>
+          <t>2349083228650</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -4920,32 +5561,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Ms </t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Uzoma</t>
+          <t>Olurankise</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Rachael</t>
+          <t>Judith</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>17 Sam Ogegbo Road</t>
+          <t>11 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2347083475377</t>
+          <t>2348036763996</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -4960,25 +5606,1070 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>Omotayo</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Christopher</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>19 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2348023260295</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>13/08/2025</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Onyeukwu</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikechukwu </t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>18 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2348036295974</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>12/03/2025</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Opeyemi</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Akanmu</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1 Adeogun Street</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2348033635600</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>22/06/2025</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mr </t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Osahon</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lambert </t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>8 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2348066860123</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>12/07/2025</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Osanyintade</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Temidayo</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>7A Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2348037125979</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Osunkunle</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Oluwatobi</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>19A Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2349024009331</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>28/07/2025</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Osunkunle</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Oluwatobi</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>19A Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2349024009331</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>17/07/2025</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Osunleye</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ayoola</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>6 Adeogun Street</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2348134654792</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>31/12/2024</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>36,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Otite</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Fred </t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>19 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2348158169490</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>28/07/2025</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Owolabi</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Abimbola</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>13 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2349163656777</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>26/04/2025</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Oyalami</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Kemi</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>4 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2348089296998</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>28/02/2025</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Oyelehin</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Oluwatosin</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>7A Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2348084586119</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>16/01/2025</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Oyemah</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Hope</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>21 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2348153992720</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ronke</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Balogun</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>17 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2348075000362</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>13/05/2025</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Daddy</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Shomorin</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Jibewa</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>5 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2348023610501</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>01/02/2025</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Siyaka</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>24 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2348024790662</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>29/11/2025</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Talabi</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Yinka</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>7 Martins Street</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2348034709952</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>09/11/2025</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tokunboh</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Daniju</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>3 Olanpejo Street</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2348068687060</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Tokunboh</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Daniju</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>3 Olanpejo Street</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2348068687060</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tolulope </t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Akinjise</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>23 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2348169696476</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tolulope </t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Akinjise</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>23 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2348169696476</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mr </t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tomisin</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Obakpolo</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>7 Martins Street</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2349084860718</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>17/07/2025</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ugo</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2347064681113</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>02/11/2025</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ukaha</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Eberechi</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>16 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2348064383418</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>18/03/2025</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ututu</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cletus</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>8 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2348039727477</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>07/02/2025</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Mrs</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Uzoma</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Rachael</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>17 Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2347083475377</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yesua </t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>22 Jibewa Shomorin Close</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>2348133398748</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>11/04/2025</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
